--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.4987699868895</v>
+        <v>5.768550122869544</v>
       </c>
       <c r="D2" t="n">
-        <v>33.36419542154745</v>
+        <v>5.421681756001461</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F2" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.72297692957005</v>
+        <v>3.042483751055133</v>
       </c>
       <c r="D3" t="n">
-        <v>23.21354830136817</v>
+        <v>3.772201598972327</v>
       </c>
       <c r="E3" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F3" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.24772432114555</v>
+        <v>5.727755202186152</v>
       </c>
       <c r="D4" t="n">
-        <v>13.47062821914079</v>
+        <v>2.188977085610378</v>
       </c>
       <c r="E4" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F4" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.64895479741779</v>
+        <v>4.005455154580391</v>
       </c>
       <c r="D5" t="n">
-        <v>24.79037268740478</v>
+        <v>4.028435561703278</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F5" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.59226571581583</v>
+        <v>1.883743178820072</v>
       </c>
       <c r="D6" t="n">
-        <v>11.3260546479738</v>
+        <v>1.840483880295742</v>
       </c>
       <c r="E6" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F6" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.91336486854934</v>
+        <v>3.398421791139268</v>
       </c>
       <c r="D7" t="n">
-        <v>20.68905095888206</v>
+        <v>3.361970780818335</v>
       </c>
       <c r="E7" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F7" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.36986218750622</v>
+        <v>0.7101026054697608</v>
       </c>
       <c r="D8" t="n">
-        <v>4.228595999938068</v>
+        <v>0.687146849989936</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F8" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.04813173146184</v>
+        <v>3.907821406362549</v>
       </c>
       <c r="D9" t="n">
-        <v>23.10475708304681</v>
+        <v>3.754523025995106</v>
       </c>
       <c r="E9" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F9" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1559686378436</v>
+        <v>2.787844903649585</v>
       </c>
       <c r="D10" t="n">
-        <v>17.05067173296135</v>
+        <v>2.770734156606219</v>
       </c>
       <c r="E10" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F10" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.432002743250782</v>
+        <v>0.5577004457782521</v>
       </c>
       <c r="D11" t="n">
-        <v>19.41582973875813</v>
+        <v>3.155072332548196</v>
       </c>
       <c r="E11" t="n">
-        <v>10.5301411343177</v>
+        <v>1.711147934326627</v>
       </c>
       <c r="F11" t="n">
-        <v>7.673996786986279</v>
+        <v>1.247024477885271</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
